--- a/qualifiers.xlsx
+++ b/qualifiers.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="5">
   <si>
     <t>Начали</t>
   </si>
@@ -36,6 +36,9 @@
   </si>
   <si>
     <t>Выпали</t>
+  </si>
+  <si>
+    <t>Изменение числа:</t>
   </si>
 </sst>
 </file>
@@ -72,8 +75,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -354,7 +360,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -380,7 +386,7 @@
         <v>6</v>
       </c>
       <c r="D2">
-        <f t="shared" ref="D2:D5" si="1">SUM(B2:C2)</f>
+        <f t="shared" ref="D2:D4" si="1">SUM(B2:C2)</f>
         <v>32</v>
       </c>
     </row>
@@ -489,7 +495,7 @@
         <v>6</v>
       </c>
       <c r="C10">
-        <f t="shared" ref="C9:C11" si="4">E11/2</f>
+        <f t="shared" ref="C10:C11" si="4">E11/2</f>
         <v>10</v>
       </c>
       <c r="D10">
@@ -600,7 +606,7 @@
         <v>10</v>
       </c>
       <c r="C17">
-        <f t="shared" ref="C17:C19" si="7">E18/2</f>
+        <f t="shared" ref="C17:C18" si="7">E18/2</f>
         <v>20</v>
       </c>
       <c r="D17">
@@ -670,7 +676,21 @@
         <v>20</v>
       </c>
     </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="1"/>
+      <c r="C22">
+        <f xml:space="preserve"> SUM(B2:B20) - 166</f>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A22:B22"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="0" copies="0" r:id="rId1"/>
 </worksheet>
 </file>